--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59BE4F9-B5AD-4301-AC61-F504C3595CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BB4B30-E055-4448-B1A6-393325E93EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="58">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="4"/>
@@ -454,7 +454,18 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>坂上、斎藤、松田</t>
+    <t>tanouesoftware</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>岩本</t>
+    <rPh sb="0" eb="2">
+      <t>イワモト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>坂上、齋藤、松田</t>
     <rPh sb="0" eb="2">
       <t>サカガミ</t>
     </rPh>
@@ -467,13 +478,31 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>tanouesoftware</t>
+    <t>岩本、齋藤、塚本</t>
+    <rPh sb="0" eb="2">
+      <t>イワモト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツカモト</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>岩本</t>
+    <t>地震被害度測定アプリ</t>
     <rPh sb="0" eb="2">
-      <t>イワモト</t>
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソクテイ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -696,16 +725,16 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1543,13 +1572,15 @@
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="28" t="s">
+        <v>57</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1743,199 +1774,199 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="26"/>
-      <c r="AL5" s="26" t="s">
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-      <c r="AS5" s="26"/>
-      <c r="AT5" s="26"/>
-      <c r="AU5" s="26"/>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="26"/>
-      <c r="AX5" s="26"/>
-      <c r="AY5" s="26"/>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="26"/>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
-      <c r="BJ5" s="26"/>
-      <c r="BK5" s="26"/>
-      <c r="BL5" s="26"/>
-      <c r="BM5" s="26"/>
-      <c r="BN5" s="26"/>
-      <c r="BO5" s="26"/>
-      <c r="BP5" s="26"/>
-      <c r="BQ5" s="25" t="s">
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27"/>
+      <c r="BM5" s="27"/>
+      <c r="BN5" s="27"/>
+      <c r="BO5" s="27"/>
+      <c r="BP5" s="27"/>
+      <c r="BQ5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="BR5" s="25"/>
-      <c r="BS5" s="25"/>
-      <c r="BT5" s="25"/>
-      <c r="BU5" s="25"/>
-      <c r="BV5" s="25"/>
-      <c r="BW5" s="25"/>
-      <c r="BX5" s="25"/>
-      <c r="BY5" s="25"/>
-      <c r="BZ5" s="25"/>
-      <c r="CA5" s="25"/>
-      <c r="CB5" s="25"/>
-      <c r="CC5" s="25"/>
-      <c r="CD5" s="25"/>
-      <c r="CE5" s="25"/>
-      <c r="CF5" s="25"/>
-      <c r="CG5" s="25"/>
-      <c r="CH5" s="25"/>
-      <c r="CI5" s="25"/>
-      <c r="CJ5" s="25"/>
-      <c r="CK5" s="25"/>
-      <c r="CL5" s="25"/>
-      <c r="CM5" s="25"/>
-      <c r="CN5" s="25"/>
-      <c r="CO5" s="25"/>
-      <c r="CP5" s="25"/>
-      <c r="CQ5" s="25"/>
-      <c r="CR5" s="25"/>
-      <c r="CS5" s="25"/>
-      <c r="CT5" s="25"/>
-      <c r="CU5" s="25" t="s">
+      <c r="BR5" s="26"/>
+      <c r="BS5" s="26"/>
+      <c r="BT5" s="26"/>
+      <c r="BU5" s="26"/>
+      <c r="BV5" s="26"/>
+      <c r="BW5" s="26"/>
+      <c r="BX5" s="26"/>
+      <c r="BY5" s="26"/>
+      <c r="BZ5" s="26"/>
+      <c r="CA5" s="26"/>
+      <c r="CB5" s="26"/>
+      <c r="CC5" s="26"/>
+      <c r="CD5" s="26"/>
+      <c r="CE5" s="26"/>
+      <c r="CF5" s="26"/>
+      <c r="CG5" s="26"/>
+      <c r="CH5" s="26"/>
+      <c r="CI5" s="26"/>
+      <c r="CJ5" s="26"/>
+      <c r="CK5" s="26"/>
+      <c r="CL5" s="26"/>
+      <c r="CM5" s="26"/>
+      <c r="CN5" s="26"/>
+      <c r="CO5" s="26"/>
+      <c r="CP5" s="26"/>
+      <c r="CQ5" s="26"/>
+      <c r="CR5" s="26"/>
+      <c r="CS5" s="26"/>
+      <c r="CT5" s="26"/>
+      <c r="CU5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="CV5" s="25"/>
-      <c r="CW5" s="25"/>
-      <c r="CX5" s="25"/>
-      <c r="CY5" s="25"/>
-      <c r="CZ5" s="25"/>
-      <c r="DA5" s="25"/>
-      <c r="DB5" s="25"/>
-      <c r="DC5" s="25"/>
-      <c r="DD5" s="25"/>
-      <c r="DE5" s="25"/>
-      <c r="DF5" s="25"/>
-      <c r="DG5" s="25"/>
-      <c r="DH5" s="25"/>
-      <c r="DI5" s="25"/>
-      <c r="DJ5" s="25"/>
-      <c r="DK5" s="25"/>
-      <c r="DL5" s="25"/>
-      <c r="DM5" s="25"/>
-      <c r="DN5" s="25"/>
-      <c r="DO5" s="25"/>
-      <c r="DP5" s="25"/>
-      <c r="DQ5" s="25"/>
-      <c r="DR5" s="25"/>
-      <c r="DS5" s="25"/>
-      <c r="DT5" s="25"/>
-      <c r="DU5" s="25"/>
-      <c r="DV5" s="25"/>
-      <c r="DW5" s="25"/>
-      <c r="DX5" s="25"/>
-      <c r="DY5" s="25"/>
-      <c r="DZ5" s="26" t="s">
+      <c r="CV5" s="26"/>
+      <c r="CW5" s="26"/>
+      <c r="CX5" s="26"/>
+      <c r="CY5" s="26"/>
+      <c r="CZ5" s="26"/>
+      <c r="DA5" s="26"/>
+      <c r="DB5" s="26"/>
+      <c r="DC5" s="26"/>
+      <c r="DD5" s="26"/>
+      <c r="DE5" s="26"/>
+      <c r="DF5" s="26"/>
+      <c r="DG5" s="26"/>
+      <c r="DH5" s="26"/>
+      <c r="DI5" s="26"/>
+      <c r="DJ5" s="26"/>
+      <c r="DK5" s="26"/>
+      <c r="DL5" s="26"/>
+      <c r="DM5" s="26"/>
+      <c r="DN5" s="26"/>
+      <c r="DO5" s="26"/>
+      <c r="DP5" s="26"/>
+      <c r="DQ5" s="26"/>
+      <c r="DR5" s="26"/>
+      <c r="DS5" s="26"/>
+      <c r="DT5" s="26"/>
+      <c r="DU5" s="26"/>
+      <c r="DV5" s="26"/>
+      <c r="DW5" s="26"/>
+      <c r="DX5" s="26"/>
+      <c r="DY5" s="26"/>
+      <c r="DZ5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="EA5" s="26"/>
-      <c r="EB5" s="26"/>
-      <c r="EC5" s="26"/>
-      <c r="ED5" s="26"/>
-      <c r="EE5" s="26"/>
-      <c r="EF5" s="26"/>
-      <c r="EG5" s="26"/>
-      <c r="EH5" s="26"/>
-      <c r="EI5" s="26"/>
-      <c r="EJ5" s="26"/>
-      <c r="EK5" s="26"/>
-      <c r="EL5" s="26"/>
-      <c r="EM5" s="26"/>
-      <c r="EN5" s="26"/>
-      <c r="EO5" s="26"/>
-      <c r="EP5" s="26"/>
-      <c r="EQ5" s="26"/>
-      <c r="ER5" s="26"/>
-      <c r="ES5" s="26"/>
-      <c r="ET5" s="26"/>
-      <c r="EU5" s="26"/>
-      <c r="EV5" s="26"/>
-      <c r="EW5" s="26"/>
-      <c r="EX5" s="26"/>
-      <c r="EY5" s="26"/>
-      <c r="EZ5" s="26"/>
-      <c r="FA5" s="26"/>
-      <c r="FB5" s="26"/>
-      <c r="FC5" s="26"/>
-      <c r="FD5" s="26"/>
-      <c r="FE5" s="25" t="s">
+      <c r="EA5" s="27"/>
+      <c r="EB5" s="27"/>
+      <c r="EC5" s="27"/>
+      <c r="ED5" s="27"/>
+      <c r="EE5" s="27"/>
+      <c r="EF5" s="27"/>
+      <c r="EG5" s="27"/>
+      <c r="EH5" s="27"/>
+      <c r="EI5" s="27"/>
+      <c r="EJ5" s="27"/>
+      <c r="EK5" s="27"/>
+      <c r="EL5" s="27"/>
+      <c r="EM5" s="27"/>
+      <c r="EN5" s="27"/>
+      <c r="EO5" s="27"/>
+      <c r="EP5" s="27"/>
+      <c r="EQ5" s="27"/>
+      <c r="ER5" s="27"/>
+      <c r="ES5" s="27"/>
+      <c r="ET5" s="27"/>
+      <c r="EU5" s="27"/>
+      <c r="EV5" s="27"/>
+      <c r="EW5" s="27"/>
+      <c r="EX5" s="27"/>
+      <c r="EY5" s="27"/>
+      <c r="EZ5" s="27"/>
+      <c r="FA5" s="27"/>
+      <c r="FB5" s="27"/>
+      <c r="FC5" s="27"/>
+      <c r="FD5" s="27"/>
+      <c r="FE5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="FF5" s="25"/>
-      <c r="FG5" s="25"/>
-      <c r="FH5" s="25"/>
-      <c r="FI5" s="25"/>
-      <c r="FJ5" s="25"/>
-      <c r="FK5" s="25"/>
-      <c r="FL5" s="25"/>
-      <c r="FM5" s="25"/>
-      <c r="FN5" s="25"/>
-      <c r="FO5" s="25"/>
-      <c r="FP5" s="25"/>
-      <c r="FQ5" s="25"/>
-      <c r="FR5" s="25"/>
-      <c r="FS5" s="25"/>
-      <c r="FT5" s="25"/>
-      <c r="FU5" s="25"/>
-      <c r="FV5" s="25"/>
-      <c r="FW5" s="25"/>
-      <c r="FX5" s="25"/>
-      <c r="FY5" s="25"/>
-      <c r="FZ5" s="25"/>
-      <c r="GA5" s="25"/>
-      <c r="GB5" s="25"/>
-      <c r="GC5" s="25"/>
-      <c r="GD5" s="25"/>
-      <c r="GE5" s="25"/>
-      <c r="GF5" s="25"/>
+      <c r="FF5" s="26"/>
+      <c r="FG5" s="26"/>
+      <c r="FH5" s="26"/>
+      <c r="FI5" s="26"/>
+      <c r="FJ5" s="26"/>
+      <c r="FK5" s="26"/>
+      <c r="FL5" s="26"/>
+      <c r="FM5" s="26"/>
+      <c r="FN5" s="26"/>
+      <c r="FO5" s="26"/>
+      <c r="FP5" s="26"/>
+      <c r="FQ5" s="26"/>
+      <c r="FR5" s="26"/>
+      <c r="FS5" s="26"/>
+      <c r="FT5" s="26"/>
+      <c r="FU5" s="26"/>
+      <c r="FV5" s="26"/>
+      <c r="FW5" s="26"/>
+      <c r="FX5" s="26"/>
+      <c r="FY5" s="26"/>
+      <c r="FZ5" s="26"/>
+      <c r="GA5" s="26"/>
+      <c r="GB5" s="26"/>
+      <c r="GC5" s="26"/>
+      <c r="GD5" s="26"/>
+      <c r="GE5" s="26"/>
+      <c r="GF5" s="26"/>
     </row>
     <row r="6" spans="1:188" ht="18" customHeight="1">
       <c r="A6" s="1"/>
@@ -3281,7 +3312,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="8">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="1"/>
@@ -3472,8 +3503,8 @@
       <c r="B10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>55</v>
+      <c r="C10" s="25" t="s">
+        <v>54</v>
       </c>
       <c r="D10" s="7">
         <v>46296</v>
@@ -3882,8 +3913,8 @@
       <c r="B12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="27" t="s">
-        <v>53</v>
+      <c r="C12" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="D12" s="7">
         <v>46307</v>
@@ -3896,7 +3927,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="8">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="1"/>
@@ -4087,7 +4118,9 @@
       <c r="B13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="D13" s="7">
         <v>46307</v>
       </c>
@@ -4099,7 +4132,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="8">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="1"/>
@@ -11097,6 +11130,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
@@ -11107,7 +11149,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11314,16 +11356,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -11334,7 +11375,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11351,12 +11392,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BB4B30-E055-4448-B1A6-393325E93EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE400C7-B656-4056-9AFA-D4E1BE84364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -465,19 +465,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>坂上、齋藤、松田</t>
-    <rPh sb="0" eb="2">
-      <t>サカガミ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>マツダ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>岩本、齋藤、塚本</t>
     <rPh sb="0" eb="2">
       <t>イワモト</t>
@@ -503,6 +490,16 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ソクテイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>坂上、松田</t>
+    <rPh sb="0" eb="2">
+      <t>サカガミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マツダ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -728,14 +725,14 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1572,8 +1569,8 @@
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>57</v>
+      <c r="B4" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
@@ -1774,199 +1771,199 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27" t="s">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BG5" s="27"/>
-      <c r="BH5" s="27"/>
-      <c r="BI5" s="27"/>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27"/>
-      <c r="BM5" s="27"/>
-      <c r="BN5" s="27"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="27"/>
-      <c r="BQ5" s="26" t="s">
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="BR5" s="26"/>
-      <c r="BS5" s="26"/>
-      <c r="BT5" s="26"/>
-      <c r="BU5" s="26"/>
-      <c r="BV5" s="26"/>
-      <c r="BW5" s="26"/>
-      <c r="BX5" s="26"/>
-      <c r="BY5" s="26"/>
-      <c r="BZ5" s="26"/>
-      <c r="CA5" s="26"/>
-      <c r="CB5" s="26"/>
-      <c r="CC5" s="26"/>
-      <c r="CD5" s="26"/>
-      <c r="CE5" s="26"/>
-      <c r="CF5" s="26"/>
-      <c r="CG5" s="26"/>
-      <c r="CH5" s="26"/>
-      <c r="CI5" s="26"/>
-      <c r="CJ5" s="26"/>
-      <c r="CK5" s="26"/>
-      <c r="CL5" s="26"/>
-      <c r="CM5" s="26"/>
-      <c r="CN5" s="26"/>
-      <c r="CO5" s="26"/>
-      <c r="CP5" s="26"/>
-      <c r="CQ5" s="26"/>
-      <c r="CR5" s="26"/>
-      <c r="CS5" s="26"/>
-      <c r="CT5" s="26"/>
-      <c r="CU5" s="26" t="s">
+      <c r="BR5" s="27"/>
+      <c r="BS5" s="27"/>
+      <c r="BT5" s="27"/>
+      <c r="BU5" s="27"/>
+      <c r="BV5" s="27"/>
+      <c r="BW5" s="27"/>
+      <c r="BX5" s="27"/>
+      <c r="BY5" s="27"/>
+      <c r="BZ5" s="27"/>
+      <c r="CA5" s="27"/>
+      <c r="CB5" s="27"/>
+      <c r="CC5" s="27"/>
+      <c r="CD5" s="27"/>
+      <c r="CE5" s="27"/>
+      <c r="CF5" s="27"/>
+      <c r="CG5" s="27"/>
+      <c r="CH5" s="27"/>
+      <c r="CI5" s="27"/>
+      <c r="CJ5" s="27"/>
+      <c r="CK5" s="27"/>
+      <c r="CL5" s="27"/>
+      <c r="CM5" s="27"/>
+      <c r="CN5" s="27"/>
+      <c r="CO5" s="27"/>
+      <c r="CP5" s="27"/>
+      <c r="CQ5" s="27"/>
+      <c r="CR5" s="27"/>
+      <c r="CS5" s="27"/>
+      <c r="CT5" s="27"/>
+      <c r="CU5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="CV5" s="26"/>
-      <c r="CW5" s="26"/>
-      <c r="CX5" s="26"/>
-      <c r="CY5" s="26"/>
-      <c r="CZ5" s="26"/>
-      <c r="DA5" s="26"/>
-      <c r="DB5" s="26"/>
-      <c r="DC5" s="26"/>
-      <c r="DD5" s="26"/>
-      <c r="DE5" s="26"/>
-      <c r="DF5" s="26"/>
-      <c r="DG5" s="26"/>
-      <c r="DH5" s="26"/>
-      <c r="DI5" s="26"/>
-      <c r="DJ5" s="26"/>
-      <c r="DK5" s="26"/>
-      <c r="DL5" s="26"/>
-      <c r="DM5" s="26"/>
-      <c r="DN5" s="26"/>
-      <c r="DO5" s="26"/>
-      <c r="DP5" s="26"/>
-      <c r="DQ5" s="26"/>
-      <c r="DR5" s="26"/>
-      <c r="DS5" s="26"/>
-      <c r="DT5" s="26"/>
-      <c r="DU5" s="26"/>
-      <c r="DV5" s="26"/>
-      <c r="DW5" s="26"/>
-      <c r="DX5" s="26"/>
-      <c r="DY5" s="26"/>
-      <c r="DZ5" s="27" t="s">
+      <c r="CV5" s="27"/>
+      <c r="CW5" s="27"/>
+      <c r="CX5" s="27"/>
+      <c r="CY5" s="27"/>
+      <c r="CZ5" s="27"/>
+      <c r="DA5" s="27"/>
+      <c r="DB5" s="27"/>
+      <c r="DC5" s="27"/>
+      <c r="DD5" s="27"/>
+      <c r="DE5" s="27"/>
+      <c r="DF5" s="27"/>
+      <c r="DG5" s="27"/>
+      <c r="DH5" s="27"/>
+      <c r="DI5" s="27"/>
+      <c r="DJ5" s="27"/>
+      <c r="DK5" s="27"/>
+      <c r="DL5" s="27"/>
+      <c r="DM5" s="27"/>
+      <c r="DN5" s="27"/>
+      <c r="DO5" s="27"/>
+      <c r="DP5" s="27"/>
+      <c r="DQ5" s="27"/>
+      <c r="DR5" s="27"/>
+      <c r="DS5" s="27"/>
+      <c r="DT5" s="27"/>
+      <c r="DU5" s="27"/>
+      <c r="DV5" s="27"/>
+      <c r="DW5" s="27"/>
+      <c r="DX5" s="27"/>
+      <c r="DY5" s="27"/>
+      <c r="DZ5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="EA5" s="27"/>
-      <c r="EB5" s="27"/>
-      <c r="EC5" s="27"/>
-      <c r="ED5" s="27"/>
-      <c r="EE5" s="27"/>
-      <c r="EF5" s="27"/>
-      <c r="EG5" s="27"/>
-      <c r="EH5" s="27"/>
-      <c r="EI5" s="27"/>
-      <c r="EJ5" s="27"/>
-      <c r="EK5" s="27"/>
-      <c r="EL5" s="27"/>
-      <c r="EM5" s="27"/>
-      <c r="EN5" s="27"/>
-      <c r="EO5" s="27"/>
-      <c r="EP5" s="27"/>
-      <c r="EQ5" s="27"/>
-      <c r="ER5" s="27"/>
-      <c r="ES5" s="27"/>
-      <c r="ET5" s="27"/>
-      <c r="EU5" s="27"/>
-      <c r="EV5" s="27"/>
-      <c r="EW5" s="27"/>
-      <c r="EX5" s="27"/>
-      <c r="EY5" s="27"/>
-      <c r="EZ5" s="27"/>
-      <c r="FA5" s="27"/>
-      <c r="FB5" s="27"/>
-      <c r="FC5" s="27"/>
-      <c r="FD5" s="27"/>
-      <c r="FE5" s="26" t="s">
+      <c r="EA5" s="28"/>
+      <c r="EB5" s="28"/>
+      <c r="EC5" s="28"/>
+      <c r="ED5" s="28"/>
+      <c r="EE5" s="28"/>
+      <c r="EF5" s="28"/>
+      <c r="EG5" s="28"/>
+      <c r="EH5" s="28"/>
+      <c r="EI5" s="28"/>
+      <c r="EJ5" s="28"/>
+      <c r="EK5" s="28"/>
+      <c r="EL5" s="28"/>
+      <c r="EM5" s="28"/>
+      <c r="EN5" s="28"/>
+      <c r="EO5" s="28"/>
+      <c r="EP5" s="28"/>
+      <c r="EQ5" s="28"/>
+      <c r="ER5" s="28"/>
+      <c r="ES5" s="28"/>
+      <c r="ET5" s="28"/>
+      <c r="EU5" s="28"/>
+      <c r="EV5" s="28"/>
+      <c r="EW5" s="28"/>
+      <c r="EX5" s="28"/>
+      <c r="EY5" s="28"/>
+      <c r="EZ5" s="28"/>
+      <c r="FA5" s="28"/>
+      <c r="FB5" s="28"/>
+      <c r="FC5" s="28"/>
+      <c r="FD5" s="28"/>
+      <c r="FE5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="FF5" s="26"/>
-      <c r="FG5" s="26"/>
-      <c r="FH5" s="26"/>
-      <c r="FI5" s="26"/>
-      <c r="FJ5" s="26"/>
-      <c r="FK5" s="26"/>
-      <c r="FL5" s="26"/>
-      <c r="FM5" s="26"/>
-      <c r="FN5" s="26"/>
-      <c r="FO5" s="26"/>
-      <c r="FP5" s="26"/>
-      <c r="FQ5" s="26"/>
-      <c r="FR5" s="26"/>
-      <c r="FS5" s="26"/>
-      <c r="FT5" s="26"/>
-      <c r="FU5" s="26"/>
-      <c r="FV5" s="26"/>
-      <c r="FW5" s="26"/>
-      <c r="FX5" s="26"/>
-      <c r="FY5" s="26"/>
-      <c r="FZ5" s="26"/>
-      <c r="GA5" s="26"/>
-      <c r="GB5" s="26"/>
-      <c r="GC5" s="26"/>
-      <c r="GD5" s="26"/>
-      <c r="GE5" s="26"/>
-      <c r="GF5" s="26"/>
+      <c r="FF5" s="27"/>
+      <c r="FG5" s="27"/>
+      <c r="FH5" s="27"/>
+      <c r="FI5" s="27"/>
+      <c r="FJ5" s="27"/>
+      <c r="FK5" s="27"/>
+      <c r="FL5" s="27"/>
+      <c r="FM5" s="27"/>
+      <c r="FN5" s="27"/>
+      <c r="FO5" s="27"/>
+      <c r="FP5" s="27"/>
+      <c r="FQ5" s="27"/>
+      <c r="FR5" s="27"/>
+      <c r="FS5" s="27"/>
+      <c r="FT5" s="27"/>
+      <c r="FU5" s="27"/>
+      <c r="FV5" s="27"/>
+      <c r="FW5" s="27"/>
+      <c r="FX5" s="27"/>
+      <c r="FY5" s="27"/>
+      <c r="FZ5" s="27"/>
+      <c r="GA5" s="27"/>
+      <c r="GB5" s="27"/>
+      <c r="GC5" s="27"/>
+      <c r="GD5" s="27"/>
+      <c r="GE5" s="27"/>
+      <c r="GF5" s="27"/>
     </row>
     <row r="6" spans="1:188" ht="18" customHeight="1">
       <c r="A6" s="1"/>
@@ -3914,7 +3911,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" s="7">
         <v>46307</v>
@@ -4119,7 +4116,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="7">
         <v>46307</v>
@@ -11130,26 +11127,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11356,10 +11333,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11376,20 +11384,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE400C7-B656-4056-9AFA-D4E1BE84364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741CC620-6F8A-4B00-B1C8-AAA2C684CD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -458,26 +458,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>岩本</t>
-    <rPh sb="0" eb="2">
-      <t>イワモト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>岩本、齋藤、塚本</t>
-    <rPh sb="0" eb="2">
-      <t>イワモト</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ツカモト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>地震被害度測定アプリ</t>
     <rPh sb="0" eb="2">
       <t>ジシン</t>
@@ -494,12 +474,41 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>坂上、松田</t>
+    <t>齋藤、塚本</t>
     <rPh sb="0" eb="2">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツカモト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>齋藤、坂上、塚本、松田</t>
+    <rPh sb="0" eb="2">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>サカガミ</t>
     </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツカモト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マツダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>岩本、坂上、田上</t>
+    <rPh sb="0" eb="2">
+      <t>イワモト</t>
+    </rPh>
     <rPh sb="3" eb="5">
-      <t>マツダ</t>
+      <t>サカガミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タノウエ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -511,7 +520,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="d"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -577,6 +586,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF334155"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="7"/>
       <color rgb="FF334155"/>
       <name val="游ゴシック"/>
       <family val="2"/>
@@ -648,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -733,6 +749,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1570,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
@@ -3501,7 +3520,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D10" s="7">
         <v>46296</v>
@@ -3910,8 +3929,8 @@
       <c r="B12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>57</v>
+      <c r="C12" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="D12" s="7">
         <v>46307</v>
@@ -11127,6 +11146,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11333,27 +11372,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11370,23 +11408,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741CC620-6F8A-4B00-B1C8-AAA2C684CD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D47D01-DF37-4CA2-A6FC-3695ACBF7FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="58">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="4"/>
@@ -744,14 +744,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1790,199 +1790,199 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28" t="s">
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="27" t="s">
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="BR5" s="27"/>
-      <c r="BS5" s="27"/>
-      <c r="BT5" s="27"/>
-      <c r="BU5" s="27"/>
-      <c r="BV5" s="27"/>
-      <c r="BW5" s="27"/>
-      <c r="BX5" s="27"/>
-      <c r="BY5" s="27"/>
-      <c r="BZ5" s="27"/>
-      <c r="CA5" s="27"/>
-      <c r="CB5" s="27"/>
-      <c r="CC5" s="27"/>
-      <c r="CD5" s="27"/>
-      <c r="CE5" s="27"/>
-      <c r="CF5" s="27"/>
-      <c r="CG5" s="27"/>
-      <c r="CH5" s="27"/>
-      <c r="CI5" s="27"/>
-      <c r="CJ5" s="27"/>
-      <c r="CK5" s="27"/>
-      <c r="CL5" s="27"/>
-      <c r="CM5" s="27"/>
-      <c r="CN5" s="27"/>
-      <c r="CO5" s="27"/>
-      <c r="CP5" s="27"/>
-      <c r="CQ5" s="27"/>
-      <c r="CR5" s="27"/>
-      <c r="CS5" s="27"/>
-      <c r="CT5" s="27"/>
-      <c r="CU5" s="27" t="s">
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="28"/>
+      <c r="CM5" s="28"/>
+      <c r="CN5" s="28"/>
+      <c r="CO5" s="28"/>
+      <c r="CP5" s="28"/>
+      <c r="CQ5" s="28"/>
+      <c r="CR5" s="28"/>
+      <c r="CS5" s="28"/>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="CV5" s="27"/>
-      <c r="CW5" s="27"/>
-      <c r="CX5" s="27"/>
-      <c r="CY5" s="27"/>
-      <c r="CZ5" s="27"/>
-      <c r="DA5" s="27"/>
-      <c r="DB5" s="27"/>
-      <c r="DC5" s="27"/>
-      <c r="DD5" s="27"/>
-      <c r="DE5" s="27"/>
-      <c r="DF5" s="27"/>
-      <c r="DG5" s="27"/>
-      <c r="DH5" s="27"/>
-      <c r="DI5" s="27"/>
-      <c r="DJ5" s="27"/>
-      <c r="DK5" s="27"/>
-      <c r="DL5" s="27"/>
-      <c r="DM5" s="27"/>
-      <c r="DN5" s="27"/>
-      <c r="DO5" s="27"/>
-      <c r="DP5" s="27"/>
-      <c r="DQ5" s="27"/>
-      <c r="DR5" s="27"/>
-      <c r="DS5" s="27"/>
-      <c r="DT5" s="27"/>
-      <c r="DU5" s="27"/>
-      <c r="DV5" s="27"/>
-      <c r="DW5" s="27"/>
-      <c r="DX5" s="27"/>
-      <c r="DY5" s="27"/>
-      <c r="DZ5" s="28" t="s">
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28"/>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="28"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28"/>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28"/>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28"/>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="28"/>
+      <c r="DH5" s="28"/>
+      <c r="DI5" s="28"/>
+      <c r="DJ5" s="28"/>
+      <c r="DK5" s="28"/>
+      <c r="DL5" s="28"/>
+      <c r="DM5" s="28"/>
+      <c r="DN5" s="28"/>
+      <c r="DO5" s="28"/>
+      <c r="DP5" s="28"/>
+      <c r="DQ5" s="28"/>
+      <c r="DR5" s="28"/>
+      <c r="DS5" s="28"/>
+      <c r="DT5" s="28"/>
+      <c r="DU5" s="28"/>
+      <c r="DV5" s="28"/>
+      <c r="DW5" s="28"/>
+      <c r="DX5" s="28"/>
+      <c r="DY5" s="28"/>
+      <c r="DZ5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="EA5" s="28"/>
-      <c r="EB5" s="28"/>
-      <c r="EC5" s="28"/>
-      <c r="ED5" s="28"/>
-      <c r="EE5" s="28"/>
-      <c r="EF5" s="28"/>
-      <c r="EG5" s="28"/>
-      <c r="EH5" s="28"/>
-      <c r="EI5" s="28"/>
-      <c r="EJ5" s="28"/>
-      <c r="EK5" s="28"/>
-      <c r="EL5" s="28"/>
-      <c r="EM5" s="28"/>
-      <c r="EN5" s="28"/>
-      <c r="EO5" s="28"/>
-      <c r="EP5" s="28"/>
-      <c r="EQ5" s="28"/>
-      <c r="ER5" s="28"/>
-      <c r="ES5" s="28"/>
-      <c r="ET5" s="28"/>
-      <c r="EU5" s="28"/>
-      <c r="EV5" s="28"/>
-      <c r="EW5" s="28"/>
-      <c r="EX5" s="28"/>
-      <c r="EY5" s="28"/>
-      <c r="EZ5" s="28"/>
-      <c r="FA5" s="28"/>
-      <c r="FB5" s="28"/>
-      <c r="FC5" s="28"/>
-      <c r="FD5" s="28"/>
-      <c r="FE5" s="27" t="s">
+      <c r="EA5" s="29"/>
+      <c r="EB5" s="29"/>
+      <c r="EC5" s="29"/>
+      <c r="ED5" s="29"/>
+      <c r="EE5" s="29"/>
+      <c r="EF5" s="29"/>
+      <c r="EG5" s="29"/>
+      <c r="EH5" s="29"/>
+      <c r="EI5" s="29"/>
+      <c r="EJ5" s="29"/>
+      <c r="EK5" s="29"/>
+      <c r="EL5" s="29"/>
+      <c r="EM5" s="29"/>
+      <c r="EN5" s="29"/>
+      <c r="EO5" s="29"/>
+      <c r="EP5" s="29"/>
+      <c r="EQ5" s="29"/>
+      <c r="ER5" s="29"/>
+      <c r="ES5" s="29"/>
+      <c r="ET5" s="29"/>
+      <c r="EU5" s="29"/>
+      <c r="EV5" s="29"/>
+      <c r="EW5" s="29"/>
+      <c r="EX5" s="29"/>
+      <c r="EY5" s="29"/>
+      <c r="EZ5" s="29"/>
+      <c r="FA5" s="29"/>
+      <c r="FB5" s="29"/>
+      <c r="FC5" s="29"/>
+      <c r="FD5" s="29"/>
+      <c r="FE5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="FF5" s="27"/>
-      <c r="FG5" s="27"/>
-      <c r="FH5" s="27"/>
-      <c r="FI5" s="27"/>
-      <c r="FJ5" s="27"/>
-      <c r="FK5" s="27"/>
-      <c r="FL5" s="27"/>
-      <c r="FM5" s="27"/>
-      <c r="FN5" s="27"/>
-      <c r="FO5" s="27"/>
-      <c r="FP5" s="27"/>
-      <c r="FQ5" s="27"/>
-      <c r="FR5" s="27"/>
-      <c r="FS5" s="27"/>
-      <c r="FT5" s="27"/>
-      <c r="FU5" s="27"/>
-      <c r="FV5" s="27"/>
-      <c r="FW5" s="27"/>
-      <c r="FX5" s="27"/>
-      <c r="FY5" s="27"/>
-      <c r="FZ5" s="27"/>
-      <c r="GA5" s="27"/>
-      <c r="GB5" s="27"/>
-      <c r="GC5" s="27"/>
-      <c r="GD5" s="27"/>
-      <c r="GE5" s="27"/>
-      <c r="GF5" s="27"/>
+      <c r="FF5" s="28"/>
+      <c r="FG5" s="28"/>
+      <c r="FH5" s="28"/>
+      <c r="FI5" s="28"/>
+      <c r="FJ5" s="28"/>
+      <c r="FK5" s="28"/>
+      <c r="FL5" s="28"/>
+      <c r="FM5" s="28"/>
+      <c r="FN5" s="28"/>
+      <c r="FO5" s="28"/>
+      <c r="FP5" s="28"/>
+      <c r="FQ5" s="28"/>
+      <c r="FR5" s="28"/>
+      <c r="FS5" s="28"/>
+      <c r="FT5" s="28"/>
+      <c r="FU5" s="28"/>
+      <c r="FV5" s="28"/>
+      <c r="FW5" s="28"/>
+      <c r="FX5" s="28"/>
+      <c r="FY5" s="28"/>
+      <c r="FZ5" s="28"/>
+      <c r="GA5" s="28"/>
+      <c r="GB5" s="28"/>
+      <c r="GC5" s="28"/>
+      <c r="GD5" s="28"/>
+      <c r="GE5" s="28"/>
+      <c r="GF5" s="28"/>
     </row>
     <row r="6" spans="1:188" ht="18" customHeight="1">
       <c r="A6" s="1"/>
@@ -3929,7 +3929,7 @@
       <c r="B12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="7">
@@ -4339,7 +4339,9 @@
       <c r="B14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="25" t="s">
+        <v>55</v>
+      </c>
       <c r="D14" s="7">
         <v>46307</v>
       </c>
@@ -11146,6 +11148,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
@@ -11154,15 +11165,6 @@
     <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11373,20 +11375,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
     <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D47D01-DF37-4CA2-A6FC-3695ACBF7FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91F3200-9CC7-4305-8C2C-D6B2D47934EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3943,7 +3943,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="1"/>
@@ -4148,7 +4148,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="8">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="1"/>
@@ -4340,7 +4340,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" s="7">
         <v>46307</v>
@@ -4353,7 +4353,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="1"/>
@@ -11148,26 +11148,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11374,10 +11354,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11394,20 +11405,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91F3200-9CC7-4305-8C2C-D6B2D47934EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC44E66-9298-44E6-90F2-8D9272EAB970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="60">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="4"/>
@@ -509,6 +509,29 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>タノウエ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>岩本、齋藤、塚本</t>
+    <rPh sb="0" eb="2">
+      <t>イワモト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツカモト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>坂上、松田</t>
+    <rPh sb="0" eb="2">
+      <t>サカガミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マツダ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -4353,7 +4376,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="1"/>
@@ -4544,7 +4567,9 @@
       <c r="B15" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="25" t="s">
+        <v>58</v>
+      </c>
       <c r="D15" s="7">
         <v>46307</v>
       </c>
@@ -4747,7 +4772,9 @@
       <c r="B16" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="D16" s="7">
         <v>46314</v>
       </c>
@@ -11144,6 +11171,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11355,6 +11383,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
@@ -11363,15 +11400,6 @@
     <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11394,6 +11422,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -11402,12 +11438,4 @@
     <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC44E66-9298-44E6-90F2-8D9272EAB970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5BA0B2-5E3E-4528-B12A-ED991F7541C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="59">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="4"/>
@@ -522,16 +522,6 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>ツカモト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>坂上、松田</t>
-    <rPh sb="0" eb="2">
-      <t>サカガミ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>マツダ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -4581,7 +4571,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="1"/>
@@ -4773,7 +4763,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D16" s="7">
         <v>46314</v>
@@ -11176,6 +11166,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11382,27 +11392,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11419,23 +11428,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/卒業制作・開発演習ガントチャート.xlsx
+++ b/卒業制作・開発演習ガントチャート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5BA0B2-5E3E-4528-B12A-ED991F7541C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97479F69-488A-41AD-8D50-701E52B23BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="62">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="4"/>
@@ -454,10 +454,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>tanouesoftware</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>地震被害度測定アプリ</t>
     <rPh sb="0" eb="2">
       <t>ジシン</t>
@@ -522,6 +518,43 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>ツカモト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>岩本、坂上</t>
+    <rPh sb="0" eb="2">
+      <t>イワモト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サカガミ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>齋藤、塚本、松田</t>
+    <rPh sb="0" eb="2">
+      <t>サイトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツカモト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マツダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>田上</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>チーム田上</t>
+    <rPh sb="3" eb="5">
+      <t>タノウエ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -677,7 +710,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -765,6 +798,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1602,14 +1638,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>53</v>
+      <c r="E4" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3533,7 +3569,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="7">
         <v>46296</v>
@@ -3741,10 +3777,10 @@
         <v>51</v>
       </c>
       <c r="D11" s="7">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="E11" s="7">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
@@ -3943,7 +3979,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="7">
         <v>46307</v>
@@ -4148,7 +4184,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="7">
         <v>46307</v>
@@ -4558,7 +4594,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="7">
         <v>46307</v>
@@ -4776,7 +4812,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="1"/>
@@ -4967,7 +5003,9 @@
       <c r="B17" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="25" t="s">
+        <v>58</v>
+      </c>
       <c r="D17" s="7">
         <v>46314</v>
       </c>
@@ -5373,7 +5411,9 @@
       <c r="B19" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="D19" s="7">
         <v>46314</v>
       </c>
@@ -5779,7 +5819,9 @@
       <c r="B21" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="D21" s="7">
         <v>46314</v>
       </c>
@@ -11177,15 +11219,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11392,6 +11425,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF3EEADF-405C-48E4-9DBA-3ED73C479A71}">
   <ds:schemaRefs>
@@ -11404,14 +11446,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{711F21EF-C336-420D-8628-BAC810F83ECE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11428,4 +11462,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E9EDEC-9EDB-4A4C-B9D2-F27F56E0DA67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>